--- a/docs/ValueSet-ahip-disability.xlsx
+++ b/docs/ValueSet-ahip-disability.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t>Property</t>
   </si>
@@ -49,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T00:00:00-04:00</t>
+    <t>2026-08-25T00:00:00-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +86,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Based on our own list of disabilities</t>
+    <t>Used as the answer options for the functional difficulty question in the Disability Section, capturing difficulty with activities of daily living due to a physical or mental health condition.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -103,85 +104,28 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-disability-codes</t>
+  </si>
+  <si>
     <t>Concept</t>
   </si>
   <si>
-    <t>COMM</t>
-  </si>
-  <si>
-    <t>Communicating or being understood using your usual language</t>
-  </si>
-  <si>
-    <t>CONC</t>
-  </si>
-  <si>
-    <t>Concentrating, remembering, or making decisions</t>
-  </si>
-  <si>
-    <t>COOK</t>
-  </si>
-  <si>
-    <t>Cooking for oneself</t>
-  </si>
-  <si>
-    <t>DRES</t>
-  </si>
-  <si>
-    <t>Dressing or bathing</t>
-  </si>
-  <si>
-    <t>ERRA</t>
-  </si>
-  <si>
-    <t>Doing errands alone</t>
-  </si>
-  <si>
-    <t>FEED</t>
-  </si>
-  <si>
-    <t>Feeding oneself</t>
-  </si>
-  <si>
-    <t>HEAR</t>
-  </si>
-  <si>
-    <t>Hearing</t>
-  </si>
-  <si>
-    <t>SEEI</t>
-  </si>
-  <si>
-    <t>Seeing (even when wearing glasses)</t>
-  </si>
-  <si>
-    <t>UNDE</t>
-  </si>
-  <si>
-    <t>Understanding when someone speaks in your usual language</t>
-  </si>
-  <si>
-    <t>TOIL</t>
-  </si>
-  <si>
-    <t>Using the toilet</t>
-  </si>
-  <si>
-    <t>WALK</t>
-  </si>
-  <si>
-    <t>Walking or climbing stairs</t>
-  </si>
-  <si>
-    <t>NONE</t>
+    <t>LA137-2</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/ahip-demo-additional-disability-codes</t>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>PSIN</t>
@@ -196,7 +140,7 @@
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/ImplementationGuide/ahip.demo/CodeSystem/AHIPDemoAdditionalNullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
   </si>
 </sst>
 </file>
@@ -462,7 +406,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -473,120 +417,26 @@
       <c r="A1" t="s" s="1">
         <v>29</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>31</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -595,6 +445,52 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
@@ -605,7 +501,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>22</v>
@@ -613,18 +509,18 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -637,10 +533,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-disability.xlsx
+++ b/docs/ValueSet-ahip-disability.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Property</t>
   </si>
@@ -126,12 +126,6 @@
   </si>
   <si>
     <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>PSIN</t>
-  </si>
-  <si>
-    <t>Other difficulties when doing activities throughout your day (please describe)</t>
   </si>
   <si>
     <t>CNTR</t>
@@ -492,7 +486,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -517,26 +511,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/docs/ValueSet-ahip-disability.xlsx
+++ b/docs/ValueSet-ahip-disability.xlsx
@@ -10,12 +10,13 @@
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
     <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -95,7 +96,9 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Used by permission of HL7 International, all rights reserved Creative Commons License</t>
+    <t>This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc.
+This material derives from the HL7 Terminology (THO). THO is copyright ©1989+ Health Level Seven International and is made available under the CC0 designation. For more licensing information see: https://terminology.hl7.org/license.html
+This value set includes content developed through the DEMo Initiative and is subject to joint copyright of America's Health Insurance Plans (AHIP) and Health Level Seven International (HL7).</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -128,13 +131,22 @@
     <t>http://loinc.org</t>
   </si>
   <si>
+    <t>ASKU</t>
+  </si>
+  <si>
+    <t>I don't know</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v3-NullFlavor</t>
+  </si>
+  <si>
     <t>CNTR</t>
   </si>
   <si>
     <t>I choose not to respond at this time</t>
   </si>
   <si>
-    <t>http://ahip.org/demographics/CodeSystem/AHIP-Demo-Additional-NullFlavor</t>
+    <t>http://ahip.org/demographics/CodeSystem/ahip-demo-additional-nullFlavor</t>
   </si>
 </sst>
 </file>
@@ -528,4 +540,50 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>